--- a/notebooks/data/ammonia.xlsx
+++ b/notebooks/data/ammonia.xlsx
@@ -2077,7 +2077,7 @@
         <v>24</v>
       </c>
       <c r="B14">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C14" t="s">
         <v>25</v>
